--- a/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/base_consolidada_cirurgioes.xlsx
+++ b/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/base_consolidada_cirurgioes.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,10 +1651,8 @@
           <t>MARCOS CAIQUE DOS SANTOS MATIAS</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>096353876</t>
-        </is>
+      <c r="F22" t="n">
+        <v>96353876</v>
       </c>
       <c r="G22" t="n">
         <v>34753593835</v>
@@ -1713,10 +1711,8 @@
           <t>GUSTAVO DA SILVA ARRUDA</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>452147883</t>
-        </is>
+      <c r="F23" t="n">
+        <v>452147883</v>
       </c>
       <c r="G23" t="n">
         <v>41214926843</v>
@@ -1775,10 +1771,8 @@
           <t>CAMILA FREITAS DA SILVA</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>097156178</t>
-        </is>
+      <c r="F24" t="n">
+        <v>97156178</v>
       </c>
       <c r="G24" t="n">
         <v>54215065844</v>
@@ -1837,10 +1831,8 @@
           <t>JULIANA GOMES MATHEUS</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>093636061</t>
-        </is>
+      <c r="F25" t="n">
+        <v>93636061</v>
       </c>
       <c r="G25" t="n">
         <v>11726442764</v>
@@ -1899,10 +1891,8 @@
           <t>Filippo Muro Caccavale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>092748617</t>
-        </is>
+      <c r="F26" t="n">
+        <v>92748617</v>
       </c>
       <c r="G26" t="n">
         <v>26312679829</v>
@@ -1961,10 +1951,8 @@
           <t>BIANCA LUCIA MAGRI PINTO</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>087729262</t>
-        </is>
+      <c r="F27" t="n">
+        <v>87729262</v>
       </c>
       <c r="G27" t="n">
         <v>7234522611</v>
@@ -1992,6 +1980,316 @@
         </is>
       </c>
       <c r="N27" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CAMILA PATRÍCIA DA SILVA BENTO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>096737478</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>38904726808</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>17/04/1991</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>380</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>11984268949</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ERIKA MARIA DA SILVA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>094418641</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>33670620818</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>18/04/1985</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>500</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>11980812325</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LUANA DE MENDONÇA FURTADO CUNHA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>092857092</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>35420859874</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>23/06/1988</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>400</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>11912260375</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MARIA LUCIA PEREIRA PORTO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>097420124</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>14890766898</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>29/01/1966</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>380</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>11959427354</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RICHARD DA SILVA VILAPIANO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>079649693</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>36441637820</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>11/11/1988</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>450</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>11967904790</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>Dom Pedro</t>
         </is>
@@ -2008,7 +2306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3213,10 +3511,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>096353876</t>
-        </is>
+      <c r="E22" t="n">
+        <v>96353876</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3270,10 +3566,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>452147883</t>
-        </is>
+      <c r="E23" t="n">
+        <v>452147883</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3327,10 +3621,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>097156178</t>
-        </is>
+      <c r="E24" t="n">
+        <v>97156178</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3384,10 +3676,8 @@
           <t>Equipe - Cirurgião Luiz Alfredo</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>093636061</t>
-        </is>
+      <c r="E25" t="n">
+        <v>93636061</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3441,10 +3731,8 @@
           <t>Equipe - Instituto Castro</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>092748617</t>
-        </is>
+      <c r="E26" t="n">
+        <v>92748617</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3498,10 +3786,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>087729262</t>
-        </is>
+      <c r="E27" t="n">
+        <v>87729262</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,6 +3820,291 @@
         <v>11966932277</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>096737478</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CAMILA PATRÍCIA DA SILVA BENTO</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>38904726808</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>17/04/1991</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>380</v>
+      </c>
+      <c r="O28" t="n">
+        <v>11984268949</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>094418641</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ERIKA MARIA DA SILVA</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>33670620818</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>18/04/1985</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>41</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>500</v>
+      </c>
+      <c r="O29" t="n">
+        <v>11980812325</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>092857092</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>LUANA DE MENDONÇA FURTADO CUNHA</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>35420859874</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>23/06/1988</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>37</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>400</v>
+      </c>
+      <c r="O30" t="n">
+        <v>11912260375</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>097420124</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MARIA LUCIA PEREIRA PORTO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>14890766898</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>29/01/1966</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>60</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>380</v>
+      </c>
+      <c r="O31" t="n">
+        <v>11959427354</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>079649693</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>RICHARD DA SILVA VILAPIANO</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>36441637820</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>11/11/1988</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>37</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>450</v>
+      </c>
+      <c r="O32" t="n">
+        <v>11967904790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/base_consolidada_cirurgioes.xlsx
+++ b/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/base_consolidada_cirurgioes.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,10 +2011,8 @@
           <t>CAMILA PATRÍCIA DA SILVA BENTO</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>096737478</t>
-        </is>
+      <c r="F28" t="n">
+        <v>96737478</v>
       </c>
       <c r="G28" t="n">
         <v>38904726808</v>
@@ -2073,10 +2071,8 @@
           <t>ERIKA MARIA DA SILVA</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>094418641</t>
-        </is>
+      <c r="F29" t="n">
+        <v>94418641</v>
       </c>
       <c r="G29" t="n">
         <v>33670620818</v>
@@ -2135,10 +2131,8 @@
           <t>LUANA DE MENDONÇA FURTADO CUNHA</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>092857092</t>
-        </is>
+      <c r="F30" t="n">
+        <v>92857092</v>
       </c>
       <c r="G30" t="n">
         <v>35420859874</v>
@@ -2197,10 +2191,8 @@
           <t>MARIA LUCIA PEREIRA PORTO DOS SANTOS</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>097420124</t>
-        </is>
+      <c r="F31" t="n">
+        <v>97420124</v>
       </c>
       <c r="G31" t="n">
         <v>14890766898</v>
@@ -2259,10 +2251,8 @@
           <t>RICHARD DA SILVA VILAPIANO</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>079649693</t>
-        </is>
+      <c r="F32" t="n">
+        <v>79649693</v>
       </c>
       <c r="G32" t="n">
         <v>36441637820</v>
@@ -2290,6 +2280,796 @@
         </is>
       </c>
       <c r="N32" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viviane Azevedo de oliveira </t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>95919032</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8895412729</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>16/06/1981</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>60</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>21964678072</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonardo cesar dos santos pacheco </t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>94340036</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14007861773</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>02/05/1967</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>60</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>21990345044</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Juliana Ferreira Junqueira Guerra</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>88988201</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5548611607</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>23/05/1958</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>120</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>11980887272</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Alessandra da Silva Rodrigues</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>87915475</v>
+      </c>
+      <c r="G36" t="n">
+        <v>29350990873</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>02/10/1980</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>380</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>11967892248</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ana Flavia de Moraes Miguel</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>97507264</v>
+      </c>
+      <c r="G37" t="n">
+        <v>19961926714</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>18/02/2000</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>380</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>(21)97552-7140</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Roberta Cavalheiro São Sabbas</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>97466941</v>
+      </c>
+      <c r="G38" t="n">
+        <v>12550149700</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>13/11/1989</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>75</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>21993640944</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>KETHLLEN LOPES FRANÇA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>82020177</v>
+      </c>
+      <c r="G39" t="n">
+        <v>18849916701</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>04/02/2001</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>380</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>21966942319</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WERONICA SILVA SOARES</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>95796652</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5322498796</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>08/11/1980</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>380</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>21966254990</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SUELEN DE CARVALHO DIAS SOUSA SOARES</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>82599167</v>
+      </c>
+      <c r="G41" t="n">
+        <v>13245574789</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>09/04/1988</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>380</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>21998162777</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LUCAS SILVA ALVES</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>088397127</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>51200118880</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>28/09/2002</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>380</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>11989775184</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DENISE DOS SANTOS FERREIRA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>074162184</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>39422138850</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>27/07/1992</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>400</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>11949646503</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GUILHERME HENRIQUE DA SILVA PONTOLLIO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>086402581</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>52877627802</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>15/04/2009</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>400</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>11987346138</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Forms Bariátrica (Cirurgiões)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>EVELYN GOMES SANTOS DE CASTRO LÉ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>087952429</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>14582143709</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16/03/1990</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>700</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>21986129699</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>Dom Pedro</t>
         </is>
@@ -2306,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3841,10 +4621,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>096737478</t>
-        </is>
+      <c r="E28" t="n">
+        <v>96737478</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3898,10 +4676,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>094418641</t>
-        </is>
+      <c r="E29" t="n">
+        <v>94418641</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3955,10 +4731,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>092857092</t>
-        </is>
+      <c r="E30" t="n">
+        <v>92857092</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4012,10 +4786,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>097420124</t>
-        </is>
+      <c r="E31" t="n">
+        <v>97420124</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,10 +4841,8 @@
           <t>Equipe - Clínica Sallet</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>079649693</t>
-        </is>
+      <c r="E32" t="n">
+        <v>79649693</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,6 +4875,731 @@
         <v>11967904790</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>95919032</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viviane Azevedo de oliveira </t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>8895412729</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>16/06/1981</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>60</v>
+      </c>
+      <c r="O33" t="n">
+        <v>21964678072</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Luiz Alfredo</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>94340036</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonardo cesar dos santos pacheco </t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>14007861773</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>02/05/1967</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>36</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>60</v>
+      </c>
+      <c r="O34" t="n">
+        <v>21990345044</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Equipe - Instituto Castro</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>88988201</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Juliana Ferreira Junqueira Guerra</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>5548611607</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>23/05/1958</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>45</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>120</v>
+      </c>
+      <c r="O35" t="n">
+        <v>11980887272</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Equipe - Instituto Castro</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>87915475</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Alessandra da Silva Rodrigues</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>29350990873</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>02/10/1980</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>45</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>380</v>
+      </c>
+      <c r="O36" t="n">
+        <v>11967892248</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>97507264</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ana Flavia de Moraes Miguel</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>19961926714</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>18/02/2000</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>26</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>380</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>(21)97552-7140</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>97466941</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Roberta Cavalheiro São Sabbas</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>12550149700</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>13/11/1989</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>36</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>75</v>
+      </c>
+      <c r="O38" t="n">
+        <v>21993640944</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>82020177</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>KETHLLEN LOPES FRANÇA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>18849916701</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>04/02/2001</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>25</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>380</v>
+      </c>
+      <c r="O39" t="n">
+        <v>21966942319</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>95796652</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>WERONICA SILVA SOARES</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>5322498796</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>08/11/1980</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>45</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>380</v>
+      </c>
+      <c r="O40" t="n">
+        <v>21966254990</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>82599167</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SUELEN DE CARVALHO DIAS SOUSA SOARES</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>13245574789</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>09/04/1988</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>38</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>380</v>
+      </c>
+      <c r="O41" t="n">
+        <v>21998162777</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>088397127</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>LUCAS SILVA ALVES</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>51200118880</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>28/09/2002</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>23</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>380</v>
+      </c>
+      <c r="O42" t="n">
+        <v>11989775184</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>074162184</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DENISE DOS SANTOS FERREIRA</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>39422138850</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>27/07/1992</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>33</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>400</v>
+      </c>
+      <c r="O43" t="n">
+        <v>11949646503</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>086402581</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>GUILHERME HENRIQUE DA SILVA PONTOLLIO</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>52877627802</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>15/04/2009</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>17</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>400</v>
+      </c>
+      <c r="O44" t="n">
+        <v>11987346138</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Captação + Navegação</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>087952429</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>EVELYN GOMES SANTOS DE CASTRO LÉ</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>14582143709</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16/03/1990</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>36</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>700</v>
+      </c>
+      <c r="O45" t="n">
+        <v>21986129699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
